--- a/src/utils/sxsyzlzq/friends/dahetao/zz_dahetao_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/dahetao/zz_dahetao_level.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12555" windowHeight="11160" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="13980" windowHeight="11415" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="蛮石" sheetId="8" r:id="rId1"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
-    <sheet name="帝国" sheetId="5" r:id="rId3"/>
+    <sheet name="帝国" sheetId="5" r:id="rId2"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
     <sheet name="禅意" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="71">
   <si>
     <t>名称</t>
   </si>
@@ -41,9 +41,6 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>愚笨鲸头鹅</t>
-  </si>
-  <si>
     <t>旷野祭师</t>
   </si>
   <si>
@@ -107,6 +104,57 @@
     <t>蛮石卡等：</t>
   </si>
   <si>
+    <t>圣殿斥候</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>增援战线</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>传记·钢铁守卫</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
     <t>洞悉之眼</t>
   </si>
   <si>
@@ -159,57 +207,6 @@
   </si>
   <si>
     <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>圣殿斥候</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>增援战线</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
-  </si>
-  <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
   </si>
   <si>
     <t>长耳庄巧姑</t>
@@ -1209,7 +1206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1233,10 +1230,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1255,63 +1252,63 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>21.3333333333333</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>19.8</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
@@ -1319,10 +1316,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
@@ -1330,10 +1327,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
@@ -1341,10 +1338,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
@@ -1352,65 +1349,65 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="C19" s="2">
+        <f>AVERAGE(C10:C16)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>22</v>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
         <v>21</v>
@@ -1418,80 +1415,58 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6</v>
-      </c>
-      <c r="C28" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C24:C28)</f>
+      <c r="C29" s="3">
+        <f>AVERAGE(C22:C26)</f>
         <v>20.6</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C28)</f>
-        <v>20.9411764705882</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
+        <v>21.4</v>
       </c>
     </row>
   </sheetData>
@@ -1501,6 +1476,289 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.4</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C12:C17)</f>
+        <v>21.8333333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3">
+        <v>8</v>
+      </c>
+      <c r="C27" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
+        <v>20.5625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D35"/>
@@ -1524,18 +1782,18 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1546,7 +1804,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1557,7 +1815,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1568,7 +1826,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1579,7 +1837,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -1600,20 +1858,20 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>20</v>
+        <v>20.1666666666667</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2">
         <v>1</v>
@@ -1624,7 +1882,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1635,7 +1893,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1646,18 +1904,18 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
@@ -1668,7 +1926,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -1679,7 +1937,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -1690,7 +1948,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2">
         <v>6</v>
@@ -1701,7 +1959,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B21" s="2">
         <v>7</v>
@@ -1722,19 +1980,19 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="2">
         <f>AVERAGE(C13:C21)</f>
-        <v>20.6666666666667</v>
+        <v>20.7777777777778</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
@@ -1745,18 +2003,18 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B28" s="3">
         <v>5</v>
       </c>
       <c r="C28" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B29" s="3">
         <v>7</v>
@@ -1777,309 +2035,26 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" s="3">
         <f>AVERAGE(C27:C29)</f>
-        <v>20</v>
+        <v>20.3333333333333</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C35" s="4">
         <f>AVERAGE(C2:C7,C13:C21,C27:C29)</f>
-        <v>20.3333333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="1">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>21.4</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C12:C17)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="3">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="3">
-        <v>8</v>
-      </c>
-      <c r="C27" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C17,C23:C27)</f>
-        <v>20</v>
+        <v>20.5</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2087,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2123,7 +2098,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2134,7 +2109,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2145,7 +2120,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -2156,7 +2131,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2167,7 +2142,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2178,7 +2153,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -2189,7 +2164,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -2200,7 +2175,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -2211,7 +2186,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -2222,7 +2197,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -2243,10 +2218,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C15" s="1">
         <f>AVERAGE(C2:C12)</f>
@@ -2256,7 +2231,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -2267,7 +2242,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2288,10 +2263,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2">
         <f>AVERAGE(C18:C19)</f>
@@ -2300,7 +2275,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -2311,7 +2286,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -2332,10 +2307,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
@@ -2344,10 +2319,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C12,C18:C19,C25:C26)</f>
